--- a/Sufficient data WITH_PO/forecast_summary_B0BSB6J39Z_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B0BSB6J39Z_WITH_PO.xlsx
@@ -515,16 +515,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
